--- a/public/credentials.xlsx
+++ b/public/credentials.xlsx
@@ -437,7 +437,7 @@
         <v>Manager@123</v>
       </c>
       <c r="E2" t="str">
-        <v>All locations</v>
+        <v>All units</v>
       </c>
     </row>
     <row r="3">
@@ -454,7 +454,7 @@
         <v>Amit@123</v>
       </c>
       <c r="E3" t="str">
-        <v>Downtown Hub</v>
+        <v>Noida</v>
       </c>
     </row>
     <row r="4">
@@ -471,7 +471,7 @@
         <v>Priya@123</v>
       </c>
       <c r="E4" t="str">
-        <v>Downtown Hub</v>
+        <v>Noida</v>
       </c>
     </row>
     <row r="5">
@@ -488,7 +488,7 @@
         <v>Rahul@123</v>
       </c>
       <c r="E5" t="str">
-        <v>Riverside</v>
+        <v>Gurgaon</v>
       </c>
     </row>
     <row r="6">
@@ -505,7 +505,7 @@
         <v>Sara@123</v>
       </c>
       <c r="E6" t="str">
-        <v>Uptown Central</v>
+        <v>Gurgaon</v>
       </c>
     </row>
     <row r="7">
@@ -522,7 +522,7 @@
         <v>John@123</v>
       </c>
       <c r="E7" t="str">
-        <v>Lakeside</v>
+        <v>Okhla</v>
       </c>
     </row>
     <row r="8">
@@ -539,7 +539,7 @@
         <v>Meera@123</v>
       </c>
       <c r="E8" t="str">
-        <v>Tech Park</v>
+        <v>Okhla</v>
       </c>
     </row>
   </sheetData>
